--- a/Result/profitability/4722.xlsx
+++ b/Result/profitability/4722.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.25</v>
       </c>
       <c r="M2" t="n">
-        <v>0.37</v>
+        <v>0.4350000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>15.29</v>
+        <v>15.8425</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.08</v>
       </c>
       <c r="M3" t="n">
-        <v>0.31125</v>
+        <v>0.39125</v>
       </c>
       <c r="N3" t="n">
-        <v>14.1375</v>
+        <v>14.8675</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.46</v>
       </c>
       <c r="M4" t="n">
-        <v>0.315</v>
+        <v>0.385</v>
       </c>
       <c r="N4" t="n">
-        <v>13.25375</v>
+        <v>14.1025</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,16 +1018,16 @@
         <v>0.11</v>
       </c>
       <c r="M5" t="n">
-        <v>0.265</v>
+        <v>0.39625</v>
       </c>
       <c r="N5" t="n">
-        <v>12.84</v>
+        <v>13.5725</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0.26625</v>
+        <v>0.2987500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>12.19125</v>
+        <v>12.5625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.19</v>
       </c>
       <c r="M7" t="n">
-        <v>0.18875</v>
+        <v>0.23875</v>
       </c>
       <c r="N7" t="n">
-        <v>11.32875</v>
+        <v>11.81</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.26</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1375</v>
+        <v>0.24375</v>
       </c>
       <c r="N8" t="n">
-        <v>10.49</v>
+        <v>11.4325</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4722</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1038</v>
+      </c>
+      <c r="D75" t="n">
+        <v>813</v>
+      </c>
+      <c r="E75" t="n">
+        <v>225</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="G75" t="n">
+        <v>126</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>12.11%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>20</v>
+      </c>
+      <c r="J75" t="n">
+        <v>145</v>
+      </c>
+      <c r="K75" t="n">
+        <v>109</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.03125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.8500000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3.863636363636364</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>7.540000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.5328621908127209</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.860000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3701831964624132</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
